--- a/assets/data/excel/gachaPools.xlsx
+++ b/assets/data/excel/gachaPools.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>废墟探索卡池</t>
+          <t>常驻融合姬池</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,17 +574,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F4" t="n">
         <v>90</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>废土幸存者们在辐射废墟中搜寻融合姬信号的核心渠道。90次探索内必定发现UR级融合姬，从第75次起信号强度逐渐增强。</t>
+          <t>常驻融合姬卡池，包含R~LE品质融合姬，90抽保底SSR品质</t>
         </is>
       </c>
     </row>

--- a/assets/data/excel/gachaPools.xlsx
+++ b/assets/data/excel/gachaPools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,36 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>pitySR</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pitySSR</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pityUR</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>softPitySRStart</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>softPitySSRStart</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>softPityURStart</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
@@ -506,6 +536,36 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -553,6 +613,36 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>SR保底次数</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SSR保底次数</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>UR保底次数</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SR软保底起始次数</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>SSR软保底起始次数</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UR软保底起始次数</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
@@ -565,7 +655,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>常驻融合姬池</t>
+          <t>融合召唤</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -577,7 +667,7 @@
         <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="F4" t="n">
         <v>90</v>
@@ -590,9 +680,27 @@
       <c r="H4" t="n">
         <v>75</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>常驻融合姬卡池，包含R~LE品质融合姬，90抽保底SSR品质</t>
+      <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" t="n">
+        <v>200</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>35</v>
+      </c>
+      <c r="N4" t="n">
+        <v>180</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>常驻融合姬卡池，SR10抽保底，SSR40抽保底，UR200抽保底</t>
         </is>
       </c>
     </row>

--- a/assets/data/excel/gachaPools.xlsx
+++ b/assets/data/excel/gachaPools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>poolItems</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +574,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -646,6 +656,11 @@
           <t>描述</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>卡池包含的融合姬ID列表</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,6 +716,11 @@
       <c r="O4" t="inlineStr">
         <is>
           <t>常驻融合姬卡池，SR10抽保底，SSR40抽保底，UR200抽保底</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
